--- a/outputs_RQ3_llm_correction/rq3_llm_correction_results_20251025_030327.xlsx
+++ b/outputs_RQ3_llm_correction/rq3_llm_correction_results_20251025_030327.xlsx
@@ -4052,7 +4052,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -4116,11 +4116,11 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -4131,7 +4131,7 @@
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -4455,7 +4455,7 @@
     <col min="11" max="11" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="22.5">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -4490,7 +4490,7 @@
         <v>23</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="21.75">
       <c r="A2" s="3" t="s">
         <v>24</v>
       </c>
@@ -4521,7 +4521,7 @@
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21.75">
       <c r="A3" s="3" t="s">
         <v>30</v>
       </c>
@@ -4548,7 +4548,7 @@
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="21.75">
       <c r="A4" s="3" t="s">
         <v>33</v>
       </c>
@@ -4579,7 +4579,7 @@
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="21.75">
       <c r="A5" s="3" t="s">
         <v>36</v>
       </c>
@@ -4610,7 +4610,7 @@
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="21.75">
       <c r="A6" s="3" t="s">
         <v>39</v>
       </c>
@@ -4641,7 +4641,7 @@
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="21.75">
       <c r="A7" s="3" t="s">
         <v>42</v>
       </c>
@@ -4672,7 +4672,7 @@
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="21.75">
       <c r="A8" s="3" t="s">
         <v>45</v>
       </c>
@@ -4703,7 +4703,7 @@
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="21.75">
       <c r="A9" s="3" t="s">
         <v>48</v>
       </c>
@@ -4734,7 +4734,7 @@
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="21.75">
       <c r="A10" s="3" t="s">
         <v>51</v>
       </c>
@@ -4761,7 +4761,7 @@
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="21.75">
       <c r="A11" s="3" t="s">
         <v>53</v>
       </c>
@@ -4792,7 +4792,7 @@
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="21.75">
       <c r="A12" s="3" t="s">
         <v>56</v>
       </c>
@@ -4823,7 +4823,7 @@
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="21.75">
       <c r="A13" s="3" t="s">
         <v>59</v>
       </c>
@@ -4854,7 +4854,7 @@
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="21.75">
       <c r="A14" s="3" t="s">
         <v>62</v>
       </c>
@@ -4885,7 +4885,7 @@
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="21.75">
       <c r="A15" s="3" t="s">
         <v>65</v>
       </c>
@@ -4916,7 +4916,7 @@
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="21.75">
       <c r="A16" s="3" t="s">
         <v>68</v>
       </c>
@@ -4943,7 +4943,7 @@
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="21.75">
       <c r="A17" s="3" t="s">
         <v>70</v>
       </c>
@@ -4974,7 +4974,7 @@
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="21.75">
       <c r="A18" s="3" t="s">
         <v>72</v>
       </c>
@@ -5005,7 +5005,7 @@
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="21.75">
       <c r="A19" s="3" t="s">
         <v>75</v>
       </c>
@@ -5036,7 +5036,7 @@
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="21.75">
       <c r="A20" s="3" t="s">
         <v>78</v>
       </c>
@@ -5067,7 +5067,7 @@
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="21.75">
       <c r="A21" s="3" t="s">
         <v>81</v>
       </c>
@@ -5098,7 +5098,7 @@
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="21.75">
       <c r="A22" s="3" t="s">
         <v>84</v>
       </c>
@@ -5125,7 +5125,7 @@
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="21.75">
       <c r="A23" s="3" t="s">
         <v>86</v>
       </c>
@@ -5156,7 +5156,7 @@
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="21.75">
       <c r="A24" s="3" t="s">
         <v>89</v>
       </c>
@@ -5187,7 +5187,7 @@
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="21.75">
       <c r="A25" s="3" t="s">
         <v>92</v>
       </c>
@@ -5218,7 +5218,7 @@
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="21.75">
       <c r="A26" s="3" t="s">
         <v>95</v>
       </c>
@@ -5249,7 +5249,7 @@
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="21.75">
       <c r="A27" s="3" t="s">
         <v>98</v>
       </c>
